--- a/data/external/FPL_Evidence_Claims_Research_Pull.xlsx
+++ b/data/external/FPL_Evidence_Claims_Research_Pull.xlsx
@@ -432,7 +432,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: md.md</t>
+          <t>sources: 2026-09-01_pull1_injuries_setpieces.md, 2026-09-01_pull2_predictedxi.md</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,6 +5671,1804 @@
       <c r="L6" t="inlineStr">
         <is>
           <t>Took over penalties from departed Salah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Antonín Kinský</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ESPN squad data</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Started both GW1-2 (5 saves, 5 conceded); Dubravka is backup with 0 appearances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Martin Dúbravka</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0 (out)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ESPN squad data</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Backup GK, 0 appearances through GW2, Kinsky clearly nailed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bart Verbruggen</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RotoWire</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>OPINION</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>No specific recent team-news confirmation found this session; based on established GK1 role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bernd Leno</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESPN / StatMuse</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Started every Fulham match GW1-2 including 30 Aug vs Sunderland.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Đorđe Petrović</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yahoo Sports / starting11</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Started GW1-2 (vs Man City, and 29 Aug match).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gabriel dos Santos Magalhães</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fantasy Football Scout</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>specialist</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Part of Arsenal's established back four alongside White, Mosquera, Calafiori.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Riccardo Calafiori</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LB / LCB</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fantasy Football Scout</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>specialist</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Arteta prefers him at left-back for attacking unpredictability; scored/assisted GW1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ezri Konsa Ngoyo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>20-45 (sub)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CB / RB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Premier League official site</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CORRECTED CLUB: now Arsenal (not Aston Villa), signed £51m from Villa 20 Aug 2026; cover at CB/RB for injured Saliba/Timber but not yet a guaranteed starter over White/Mosquera/Gabriel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trai Hume</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>RB / RWB</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ESPN / khelnow</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Started GW1-2, including 30 Aug vs Fulham.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Harry Maguire</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Guardian / Yahoo</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Started and scored in 5-2 win over Ipswich on 30 Aug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Luke Shaw</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yahoo Sports / BBC</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Started but struggled defensively; left-back flagged as a weak spot needing reinforcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Virgil van Dijk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SABC Sport / Flashscore</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Captain, started GW1 at Newcastle; no injury flags found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Marcos Senesi Barón</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0 (out)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Man City official site</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>CLUB CORRECTION: left Bournemouth on a free transfer to Tottenham in summer 2026 — no longer a Bournemouth player.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Joe Rodon</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0 (out)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Official FPL site / Yahoo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Flagged with hamstring injury on FPL site (50% chance); was part of Leeds' back three in GW1-2 when fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Adrien Truffert</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>starting11 / Yahoo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Started GW1-2 at left-back in Bournemouth's back four.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ethan Ampadu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CM (pivot)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Yahoo Sports</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Captain, expected to continue alongside Anton Stach; has started every match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bruno Fernandes</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>AM / CAM</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Guardian / BBC</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Captain, hat-trick vs Ipswich 30 Aug, penalty taker, undisputed nailed starter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bryan Mbeumo</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Yahoo Sports / BBC</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Started and scored vs Ipswich 30 Aug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Christos Tzolis</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20-45 (sub)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>LW / CF</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Premier League official site / RotoWire</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CORRECTED CLUB: signed for Arsenal as Trossard replacement; regular minutes "far from guaranteed" in a stacked forward line, though most-bought and scored in GW1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pascal Groß</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CM/AM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Squawka</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>OPINION</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>No fresh GW1-2 team news found this session; based on established set-piece/creative role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dominik Szoboszlai</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CM/AM</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BBC / Yahoo Sports</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Vice-captain, took and scored decisive penalty vs Newcastle 23 Aug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Declan Rice</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CM/DM</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AllAboutFPL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>specialist</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>OPINION</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>No fresh team-news beyond set-piece role; presumed nailed given profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Elliot Anderson</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CLUB CORRECTION: transferred from Nottingham Forest to Manchester City for £116m in July 2026; role at new club still bedding in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Enzo Fernández</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20-45 (sub)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CM/DM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ESPN / SI.com</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Left out of squad entirely for GW2 vs Brighton (2nd game in succession); Alonso cited focus/commitment issues amid Man City transfer speculation — durable role change, not just rotation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Brenden Aaronson</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>LW/AM</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Yahoo Sports</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Started GW1-2 supporting from left in Farke's settled front three.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Yéremy Pino</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>RW/AM</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>RotoWire / ESPN</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>CORRECTED: remains at Crystal Palace (moved there Aug 2025, not a fresh 2026 move); started most recent listed match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Erling Haaland</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Man City</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>RotoWire / footieguide</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>OPINION</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Undisputed first-choice striker and penalty taker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominic Calvert-Lewin</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Yahoo Sports</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Leads the line, scored in each of Leeds' past two competitive fixtures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>João Pedro Junqueira de Jesus</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>75-90</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CF/SS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SI.com</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Started in confirmed Chelsea XI vs Brighton as part of front three with Palmer and Rogers.</t>
         </is>
       </c>
     </row>
@@ -5823,7 +7621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6051,6 +7849,63 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Not a change from last season but confirmed continuity under new manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Enzo Fernández</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>frozen_out</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>left out of matchday squad two games running; Alonso cited focus/commitment amid Man City transfer speculation</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ESPN / SI.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Durable role change, not one-off rotation.</t>
         </is>
       </c>
     </row>
